--- a/PAMF_DIG F2 - monthly2026-07-30.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-30.xlsx
@@ -9320,7 +9320,7 @@
         <v>0.09</v>
       </c>
       <c r="N122" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>0.09</v>
       </c>
       <c r="N164" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>0.09</v>
       </c>
       <c r="N267" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O267" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>0.09</v>
       </c>
       <c r="N273" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O273" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
         <v>0.09</v>
       </c>
       <c r="N392" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O392" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>0.09</v>
       </c>
       <c r="N476" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O476" t="inlineStr">
         <is>

--- a/PAMF_DIG F2 - monthly2026-07-30.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-30.xlsx
@@ -5086,7 +5086,7 @@
         <v>0.09</v>
       </c>
       <c r="N64" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>0.09</v>
       </c>
       <c r="N91" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>0.09</v>
       </c>
       <c r="N92" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -16182,7 +16182,7 @@
         <v>0.09</v>
       </c>
       <c r="N216" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O216" t="inlineStr">
         <is>
@@ -16328,7 +16328,7 @@
         <v>0.09</v>
       </c>
       <c r="N218" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O218" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>0.09</v>
       </c>
       <c r="N283" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O283" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>0.09</v>
       </c>
       <c r="N347" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O347" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>0.09</v>
       </c>
       <c r="N368" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O368" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>0.09</v>
       </c>
       <c r="N386" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O386" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>0.09</v>
       </c>
       <c r="N402" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O402" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>0.09</v>
       </c>
       <c r="N446" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O446" t="inlineStr">
         <is>
@@ -33775,7 +33775,7 @@
         <v>0.09</v>
       </c>
       <c r="N457" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O457" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>0.09</v>
       </c>
       <c r="N475" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O475" t="inlineStr">
         <is>
